--- a/results/Int Task Remove ACC -0.6/Rando_8_permute.xlsx
+++ b/results/Int Task Remove ACC -0.6/Rando_8_permute.xlsx
@@ -440,227 +440,227 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6312350142920464</v>
+        <v>0.6549210709087927</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6088165696994656</v>
+        <v>0.609576543593359</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.6043153603724657</v>
+        <v>0.6096557693448693</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.6053014941208907</v>
+        <v>0.6061448819117488</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.6053014941208907</v>
+        <v>0.604842892193646</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.593773274745832</v>
+        <v>0.6172706903110745</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5931415628064762</v>
+        <v>0.6199142826230355</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.5919542235701846</v>
+        <v>0.6199142826230355</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5652764350505893</v>
+        <v>0.6110765976902377</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.5674467669262153</v>
+        <v>0.5961990834941697</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.5667754421111045</v>
+        <v>0.58834543823707</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.5697745032684985</v>
+        <v>0.5795056592315451</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.5694190344230655</v>
+        <v>0.575402672734824</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5689759635352136</v>
+        <v>0.559296112353982</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.5608804528781284</v>
+        <v>0.5444967768730608</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.5555880330723886</v>
+        <v>0.5458373324305553</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.5547196909148655</v>
+        <v>0.5395671551672989</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.5484025715213089</v>
+        <v>0.5261094222802358</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.548758040366742</v>
+        <v>0.5122951735113761</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.4943111024245872</v>
+        <v>0.5018031711241331</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.4941922637973216</v>
+        <v>0.4992763233667105</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.503511585457363</v>
+        <v>0.501052620557512</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.5137774279900741</v>
+        <v>0.4959217933638835</v>
       </c>
     </row>
     <row r="25">
@@ -670,657 +670,657 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.5137774279900741</v>
+        <v>0.4959217933638835</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.5184318536382768</v>
+        <v>0.4956455502699609</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.5217916188229217</v>
+        <v>0.4893284308764043</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.5323347514859191</v>
+        <v>0.4897203714885018</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.532925803513156</v>
+        <v>0.5101279827448407</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.5255839845317828</v>
+        <v>0.5094962708054851</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.531541446934452</v>
+        <v>0.5104438387145185</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.5269234930529136</v>
+        <v>0.5101675956205959</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.5114465505387003</v>
+        <v>0.5071278745510832</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.4902519169490757</v>
+        <v>0.5052702575360442</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.4902519169490757</v>
+        <v>0.5038098163149206</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.4902519169490757</v>
+        <v>0.5079148968843687</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.4867806423917103</v>
+        <v>0.5206199851320836</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5015518823968756</v>
+        <v>0.5022305364665315</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5005636545757234</v>
+        <v>0.5073571755147056</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5063314288905254</v>
+        <v>0.5066858506995948</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.493071760382238</v>
+        <v>0.5066858506995948</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.4933855222791887</v>
+        <v>0.4993836445939768</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.4818635851223113</v>
+        <v>0.5034845370179706</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.4818635851223113</v>
+        <v>0.5000101213515145</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.4790208813952108</v>
+        <v>0.4979638632849719</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.4749178948984898</v>
+        <v>0.5199809439381829</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.4881004317279939</v>
+        <v>0.498046230145573</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.4914945746065761</v>
+        <v>0.498046230145573</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.483095772416176</v>
+        <v>0.498046230145573</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.4913820181974921</v>
+        <v>0.4956757398184439</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5077178795419566</v>
+        <v>0.5030217469452715</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.50464482781487</v>
+        <v>0.4963533468517362</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.503933890124004</v>
+        <v>0.4886967189370487</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.503933890124004</v>
+        <v>0.4883016372158605</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.495685163145716</v>
+        <v>0.4884997015946363</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5006596329090509</v>
+        <v>0.4885799743825103</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5009807240605466</v>
+        <v>0.4736232344349319</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.476246060525682</v>
+        <v>0.4838484170555243</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.4824506235101545</v>
+        <v>0.4900102260551509</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.4927904566125582</v>
+        <v>0.486337746009919</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.4927904566125582</v>
+        <v>0.4895317304369981</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.4872572184431965</v>
+        <v>0.4801707018284745</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.4988229566212834</v>
+        <v>0.4713820530987041</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.4960303361335739</v>
+        <v>0.4731197844501139</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5317792986950437</v>
+        <v>0.4772770423316802</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5326851596555948</v>
+        <v>0.4713132977108295</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.5919439277126095</v>
+        <v>0.4776647947983233</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.5840089626312722</v>
+        <v>0.4810547495314512</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5844447042645791</v>
+        <v>0.4733918393985823</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5619252206629136</v>
+        <v>0.4626902552325642</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5619252206629136</v>
+        <v>0.4603583307448268</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.5511548811090209</v>
+        <v>0.4567317457935314</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.5429103422761873</v>
+        <v>0.4353212482069502</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.5429103422761873</v>
+        <v>0.4043568928148875</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.5137076255658359</v>
+        <v>0.4994619978151841</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.5195171068291202</v>
+        <v>0.5060595484481176</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.514427986583974</v>
+        <v>0.5168351231838282</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.5148543048900088</v>
+        <v>0.5041706948482321</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.5147115589324417</v>
+        <v>0.497764926375893</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.5227037620016544</v>
+        <v>0.5118981722235213</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.5421803834247163</v>
+        <v>0.5079942971419398</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.5369390938947309</v>
+        <v>0.5065005252632424</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.5251616798651417</v>
+        <v>0.5065005252632424</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.5181325757443556</v>
+        <v>0.5032971175088911</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5208606289896448</v>
+        <v>0.5032971175088911</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5363824195614313</v>
+        <v>0.4970707412668442</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5475748892759045</v>
+        <v>0.4971103541425994</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5157163648293506</v>
+        <v>0.4969122897638235</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5125890417174188</v>
+        <v>0.4985322295243313</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4972600803425903</v>
+        <v>0.4940664449276323</v>
       </c>
     </row>
   </sheetData>
